--- a/samples/J_科目余额表.xlsx
+++ b/samples/J_科目余额表.xlsx
@@ -438,11 +438,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -531,26 +531,26 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>应付账款-重庆钢铁设备</t>
+          <t>应付账款-重庆钢铁</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1200000</v>
+        <v>850000</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>10000000</v>
+        <v>6200000</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>10200000</v>
+        <v>6400000</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1400000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="4">
@@ -568,19 +568,19 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>850000</v>
+        <v>600000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>5000000</v>
+        <v>4500000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>4800000</v>
+        <v>4200000</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>650000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="5">
@@ -598,19 +598,79 @@
         <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>300000</v>
+        <v>500000</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>3000000</v>
+        <v>3800000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3250000</v>
+        <v>4000000</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>550000</v>
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>220204</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>应付账款-中石化</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>3550000</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>220205</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>应付账款-其他供应商</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/samples/J_科目余额表.xlsx
+++ b/samples/J_科目余额表.xlsx
@@ -442,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
